--- a/output/full_scan/batch_seq8_2026-07-16.xlsx
+++ b/output/full_scan/batch_seq8_2026-07-16.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -898,21 +898,21 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7714</v>
+        <v>8033</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>711.5153676983318</v>
+        <v>717.6719022435981</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>201.5</v>
+        <v>243</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>74.15165922690721</v>
+        <v>69.5372940233546</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>39.95334639273712</v>
+        <v>43.06569087057786</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.451536769833181</v>
+        <v>0.5113291393868251</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>6.535848922334983</v>
+        <v>7.725486342722579</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6967</v>
+        <v>7714</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>700.5311070294018</v>
+        <v>711.5153676983318</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>201.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.06279856669047</v>
+        <v>74.15165922690721</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.85626187851109</v>
+        <v>39.95334639273712</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.875318512464872</v>
+        <v>2.451536769833181</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.837631124001655</v>
+        <v>6.535848922334983</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6914</v>
+        <v>6967</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>657.8595748224769</v>
+        <v>700.5311070294018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>146.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>63.46076450657784</v>
+        <v>63.06279856669047</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>12.31609484885777</v>
+        <v>15.85626187851109</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.754432028105896</v>
+        <v>3.875318512464872</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.3148599130780978</v>
+        <v>0.837631124001655</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7799</v>
+        <v>6914</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>622.1774158715178</v>
+        <v>657.8595748224769</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>437</v>
+        <v>146.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>58.6486691043321</v>
+        <v>63.46076450657784</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>33.63846043640088</v>
+        <v>12.31609484885777</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.957750932134494</v>
+        <v>2.754432028105896</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.4786434042737184</v>
+        <v>0.3148599130780978</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8016</v>
+        <v>7799</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>613.1801168881142</v>
+        <v>622.1774158715178</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>295</v>
+        <v>437</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>42.88771837618039</v>
+        <v>58.6486691043321</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.7767411070528</v>
+        <v>33.63846043640088</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.3862030195327906</v>
+        <v>1.957750932134494</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-5.692704692630169</v>
+        <v>-0.4786434042737184</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6901</v>
+        <v>8016</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>598.5406837772148</v>
+        <v>613.1801168881142</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>19.1</v>
+        <v>295</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.37846164778981</v>
+        <v>42.88771837618039</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>47.98887823289961</v>
+        <v>29.7767411070528</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.384722698614468</v>
+        <v>0.3862030195327906</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.1023306443578226</v>
+        <v>-5.692704692630169</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8046</v>
+        <v>7795</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>590.2498271238979</v>
+        <v>610.6467624827147</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1275</v>
+        <v>563</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>61.41846452532512</v>
+        <v>58.15738000753326</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>22.68774384822818</v>
+        <v>30.03185938046345</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.929153099020842</v>
+        <v>0.3016658924790279</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>20.09196512634582</v>
+        <v>-2.912167343821821</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7828</v>
+        <v>6901</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>576.7566402778917</v>
+        <v>598.5406837772148</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2160</v>
+        <v>19.1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.07073630614283</v>
+        <v>58.37846164778981</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>26.05033623226309</v>
+        <v>47.98887823289961</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.807062168206263</v>
+        <v>0.384722698614468</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>-26.65173838379709</v>
+        <v>-0.1023306443578226</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6863</v>
+        <v>8046</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>572.7001695704651</v>
+        <v>590.2498271238979</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>105</v>
+        <v>1275</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.59180374377647</v>
+        <v>61.41846452532512</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>25.71636925638266</v>
+        <v>22.68774384822818</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.7366901082261059</v>
+        <v>0.929153099020842</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>2.007581396342214</v>
+        <v>20.09196512634582</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8024</v>
+        <v>7828</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>560.4475176728582</v>
+        <v>576.7566402778917</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>17.1</v>
+        <v>2160</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>67.44992138399064</v>
+        <v>57.07073630614283</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>40.61273904434823</v>
+        <v>26.05033623226309</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.735502536986384</v>
+        <v>1.807062168206263</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.08817410065983181</v>
+        <v>-26.65173838379709</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8039</v>
+        <v>6863</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>557.4860589237361</v>
+        <v>572.7001695704651</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>199.5</v>
+        <v>105</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>72.94576230080263</v>
+        <v>64.59180374377647</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24.91336647000232</v>
+        <v>25.71636925638266</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.159578503873472</v>
+        <v>0.7366901082261059</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>5.383129485503499</v>
+        <v>2.007581396342214</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6937</v>
+        <v>8024</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>535.6024624485005</v>
+        <v>560.4475176728582</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>288.5</v>
+        <v>17.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.23564866234949</v>
+        <v>67.44992138399064</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>12.45766205597708</v>
+        <v>40.61273904434823</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.072669232863463</v>
+        <v>0.735502536986384</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.438358019207773</v>
+        <v>0.08817410065983181</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7788</v>
+        <v>8039</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>520.2584588525467</v>
+        <v>557.4860589237361</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>261</v>
+        <v>199.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>55.60764481436542</v>
+        <v>72.94576230080263</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>25.78220478757476</v>
+        <v>24.91336647000232</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5765168757793718</v>
+        <v>1.159578503873472</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-1.023731094527562</v>
+        <v>5.383129485503499</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7715</v>
+        <v>6937</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>473.0309577808138</v>
+        <v>535.6024624485005</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>36.35</v>
+        <v>288.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>61.12041831326544</v>
+        <v>56.23564866234949</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>42.52482446156744</v>
+        <v>12.45766205597708</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.1548963825401208</v>
+        <v>2.072669232863463</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0175631702748313</v>
+        <v>1.438358019207773</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7827</v>
+        <v>7788</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>468.2984331921319</v>
+        <v>520.2584588525467</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>169.5</v>
+        <v>261</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>53.72136571538727</v>
+        <v>55.60764481436542</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>20.07734093064935</v>
+        <v>25.78220478757476</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.2507893513141209</v>
+        <v>0.5765168757793718</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.8117188205712873</v>
+        <v>-1.023731094527562</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7821</v>
+        <v>7715</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>465.0753750205769</v>
+        <v>473.0309577808138</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>41.6</v>
+        <v>36.35</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>42.59724077430875</v>
+        <v>61.12041831326544</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.30219296628488</v>
+        <v>42.52482446156744</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.491921059493656</v>
+        <v>0.1548963825401208</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0746599752957184</v>
+        <v>-0.0175631702748313</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8043</v>
+        <v>7827</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>462.0261518207244</v>
+        <v>468.2984331921319</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>153</v>
+        <v>169.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>39.84899822856585</v>
+        <v>53.72136571538727</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23.24769593717981</v>
+        <v>20.07734093064935</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7455648213174615</v>
+        <v>0.2507893513141209</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-7.881416505952402</v>
+        <v>-0.8117188205712873</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8042</v>
+        <v>7821</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>459.4867587259694</v>
+        <v>465.0753750205769</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>143.5</v>
+        <v>41.6</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>41.32175672785687</v>
+        <v>42.59724077430875</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>21.55446894066511</v>
+        <v>29.30219296628488</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6483874021434947</v>
+        <v>1.491921059493656</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-7.782152372369113</v>
+        <v>0.0746599752957184</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6923</v>
+        <v>8043</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>457.7991373308209</v>
+        <v>462.0261518207244</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>78.90000000000001</v>
+        <v>153</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>53.05989578342841</v>
+        <v>39.84899822856585</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>13.47522285403933</v>
+        <v>23.24769593717981</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.691475351550052</v>
+        <v>0.7455648213174615</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.4659239176653241</v>
+        <v>-7.881416505952402</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6919</v>
+        <v>8042</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>452.5743468455103</v>
+        <v>459.4867587259694</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>113.5</v>
+        <v>143.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>62.41252993822221</v>
+        <v>41.32175672785687</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.46738334806827</v>
+        <v>21.55446894066511</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.9150954071467994</v>
+        <v>0.6483874021434947</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.140669634759322</v>
+        <v>-7.782152372369113</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7786</v>
+        <v>6923</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>449.1360007253666</v>
+        <v>457.7991373308209</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>131</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.30071750775242</v>
+        <v>53.05989578342841</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>17.22114637633943</v>
+        <v>13.47522285403933</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.3398318433992202</v>
+        <v>1.691475351550052</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.7948765525231382</v>
+        <v>0.4659239176653241</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7717</v>
+        <v>6919</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>448.324322681616</v>
+        <v>452.5743468455103</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>485</v>
+        <v>113.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46.43217876065061</v>
+        <v>62.41252993822221</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.52094052462552</v>
+        <v>19.46738334806827</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.329953836699718</v>
+        <v>0.9150954071467994</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>13.79165533957381</v>
+        <v>1.140669634759322</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7402</v>
+        <v>7786</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>447.5653339698296</v>
+        <v>449.1360007253666</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>127.5</v>
+        <v>131</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.69940425608115</v>
+        <v>57.30071750775242</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>33.70291083562414</v>
+        <v>17.22114637633943</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6565333969829574</v>
+        <v>0.3398318433992202</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.262492381733475</v>
+        <v>0.7948765525231382</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7722</v>
+        <v>7717</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>439.0280676436437</v>
+        <v>448.324322681616</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>313.5</v>
+        <v>485</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>50.72200451986067</v>
+        <v>46.43217876065061</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>31.70910403274678</v>
+        <v>21.52094052462552</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4102705557915112</v>
+        <v>1.329953836699718</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-2.576491871710954</v>
+        <v>13.79165533957381</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7631</v>
+        <v>7402</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>429.0663723381305</v>
+        <v>447.5653339698296</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>144.5</v>
+        <v>127.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>49.8541789455475</v>
+        <v>55.69940425608115</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>14.3998527754608</v>
+        <v>33.70291083562414</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.1781572181032976</v>
+        <v>0.6565333969829574</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-2.513689210436326</v>
+        <v>1.262492381733475</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6944</v>
+        <v>7722</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>426.9269791523077</v>
+        <v>439.0280676436437</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1035</v>
+        <v>313.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>56.87420564464968</v>
+        <v>50.72200451986067</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11.50956812151791</v>
+        <v>31.70910403274678</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7258575766936346</v>
+        <v>0.4102705557915112</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.979332757232168</v>
+        <v>-2.576491871710954</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6928</v>
+        <v>7631</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>425.0193337201838</v>
+        <v>429.0663723381305</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>51.5</v>
+        <v>144.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>50.35002563685699</v>
+        <v>49.8541789455475</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>32.17180468584224</v>
+        <v>14.3998527754608</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4167835386752176</v>
+        <v>0.1781572181032976</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.1568742735282613</v>
+        <v>-2.513689210436326</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7791</v>
+        <v>6944</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>418.9722067275241</v>
+        <v>426.9269791523077</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>63.5</v>
+        <v>1035</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>53.50536750317093</v>
+        <v>56.87420564464968</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>12.98727516751906</v>
+        <v>11.50956812151791</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2.185767716168348</v>
+        <v>0.7258575766936346</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.23806689972497</v>
+        <v>1.979332757232168</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7839</v>
+        <v>6928</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>409.4070159575428</v>
+        <v>425.0193337201838</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>44.5</v>
+        <v>51.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45.19793427379516</v>
+        <v>50.35002563685699</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>11.4895343951476</v>
+        <v>32.17180468584224</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3412808195516407</v>
+        <v>0.4167835386752176</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.2948704198267138</v>
+        <v>-0.1568742735282613</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6913</v>
+        <v>7791</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>401.9221893098638</v>
+        <v>418.9722067275241</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>127</v>
+        <v>63.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.61645282434775</v>
+        <v>53.50536750317093</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14.97148026802906</v>
+        <v>12.98727516751906</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.57175604148313</v>
+        <v>2.185767716168348</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.9526657074376296</v>
+        <v>0.23806689972497</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6994</v>
+        <v>8021</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>388.7885704941321</v>
+        <v>411.705858032616</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>40.6</v>
+        <v>505</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>30.80621119235961</v>
+        <v>48.3200041041675</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>30.30500566815811</v>
+        <v>14.98978784510011</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.1670359568351209</v>
+        <v>0.2355944383107726</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0743032320614069</v>
+        <v>-8.390209972203778</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7751</v>
+        <v>7839</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>387.4838403161661</v>
+        <v>409.4070159575428</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1240</v>
+        <v>44.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>40.18096074556112</v>
+        <v>45.19793427379516</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12.87381026593502</v>
+        <v>11.4895343951476</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8887602629840511</v>
+        <v>0.3412808195516407</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-9.810284952966754</v>
+        <v>0.2948704198267138</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7712</v>
+        <v>6913</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>380.8500932592588</v>
+        <v>401.9221893098638</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>160.5</v>
+        <v>127</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>40.27183336282398</v>
+        <v>52.61645282434775</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>28.81155260118127</v>
+        <v>14.97148026802906</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2674527764452377</v>
+        <v>0.57175604148313</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-6.016109045956783</v>
+        <v>0.9526657074376296</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6997</v>
+        <v>6994</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>378.7756728574134</v>
+        <v>388.7885704941321</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>73</v>
+        <v>40.6</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.81043356857355</v>
+        <v>30.80621119235961</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>8.957246141505326</v>
+        <v>30.30500566815811</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.8722301291307826</v>
+        <v>0.1670359568351209</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.115523668600188</v>
+        <v>-0.0743032320614069</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8047</v>
+        <v>7751</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>378.2242346296794</v>
+        <v>387.4838403161661</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>43.25</v>
+        <v>1240</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>40.1445134132523</v>
+        <v>40.18096074556112</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10.24214248082967</v>
+        <v>12.87381026593502</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6341499835121419</v>
+        <v>0.8887602629840511</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.5294940140595414</v>
+        <v>-9.810284952966754</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6869</v>
+        <v>7712</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>378.068976844278</v>
+        <v>380.8500932592588</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>160.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>38.32744997275871</v>
+        <v>40.27183336282398</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.78460765485377</v>
+        <v>28.81155260118127</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6095161734454217</v>
+        <v>0.2674527764452377</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1015372848819993</v>
+        <v>-6.016109045956783</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6873</v>
+        <v>6997</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>377.1524071193671</v>
+        <v>378.7756728574134</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>86.8</v>
+        <v>73</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>52.02553197672273</v>
+        <v>50.81043356857355</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16.36337069025765</v>
+        <v>8.957246141505326</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.3820877333332462</v>
+        <v>0.8722301291307826</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.5675027933095913</v>
+        <v>0.115523668600188</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7770</v>
+        <v>8047</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>376.8865823903579</v>
+        <v>378.2242346296794</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>41.75</v>
+        <v>43.25</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>46.06148482600697</v>
+        <v>40.1445134132523</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>5.787069619094482</v>
+        <v>10.24214248082967</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.6871942746528085</v>
+        <v>0.6341499835121419</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.004108216959053</v>
+        <v>-0.5294940140595414</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6953</v>
+        <v>6869</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>374.2794066724909</v>
+        <v>378.068976844278</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>228</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45.49219803800749</v>
+        <v>38.32744997275871</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10.52908237986544</v>
+        <v>22.78460765485377</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5822967659096381</v>
+        <v>0.6095161734454217</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0144042801508872</v>
+        <v>0.1015372848819993</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6861</v>
+        <v>6873</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>372.1398628503942</v>
+        <v>377.1524071193671</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>250</v>
+        <v>86.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>33.85044698805891</v>
+        <v>52.02553197672273</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>19.07829499827683</v>
+        <v>16.36337069025765</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.522109826607774</v>
+        <v>0.3820877333332462</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-8.527116574758224</v>
+        <v>0.5675027933095913</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8040</v>
+        <v>7770</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>370.5169990661321</v>
+        <v>376.8865823903579</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>82.5</v>
+        <v>41.75</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>36.15540871859072</v>
+        <v>46.06148482600697</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>24.32393671853001</v>
+        <v>5.787069619094482</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.1613645320375343</v>
+        <v>0.6871942746528085</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-2.782975248833719</v>
+        <v>0.004108216959053</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7747</v>
+        <v>6953</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>368.596082826619</v>
+        <v>374.2794066724909</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>115.5</v>
+        <v>228</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>40.85221352939732</v>
+        <v>45.49219803800749</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10.3671442406215</v>
+        <v>10.52908237986544</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2182852575809009</v>
+        <v>0.5822967659096381</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-2.068874609958952</v>
+        <v>-0.0144042801508872</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7818</v>
+        <v>6861</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>368.2617002974935</v>
+        <v>372.1398628503942</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>69.7</v>
+        <v>250</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.83012832992171</v>
+        <v>33.85044698805891</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>26.30358410525784</v>
+        <v>19.07829499827683</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7566463403578961</v>
+        <v>1.522109826607774</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.083057575836871</v>
+        <v>-8.527116574758224</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8045</v>
+        <v>8040</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>364.2622427168199</v>
+        <v>370.5169990661321</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>60.5</v>
+        <v>82.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48.2427049083626</v>
+        <v>36.15540871859072</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11.69970050587381</v>
+        <v>24.32393671853001</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3.471514435895034</v>
+        <v>0.1613645320375343</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.2616239759215704</v>
+        <v>-2.782975248833719</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6934</v>
+        <v>7747</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>363.5354367537494</v>
+        <v>368.596082826619</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>81</v>
+        <v>115.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>67.31572619832953</v>
+        <v>40.85221352939732</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>24.13674768078842</v>
+        <v>10.3671442406215</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3063228187683225</v>
+        <v>0.2182852575809009</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.878203271211565</v>
+        <v>-2.068874609958952</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6887</v>
+        <v>7818</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>339.2026394759769</v>
+        <v>368.2617002974935</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>37.55</v>
+        <v>69.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>55.54526063761976</v>
+        <v>54.83012832992171</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>11.4265929579154</v>
+        <v>26.30358410525784</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.02026394759769</v>
+        <v>0.7566463403578961</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.4006171814646344</v>
+        <v>1.083057575836871</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7711</v>
+        <v>8045</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>337.4587082196859</v>
+        <v>364.2622427168199</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>314</v>
+        <v>60.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>38.7657017355621</v>
+        <v>48.2427049083626</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>23.93324328787323</v>
+        <v>11.69970050587381</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4203463664556483</v>
+        <v>3.471514435895034</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.626785165625563</v>
+        <v>0.2616239759215704</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7823</v>
+        <v>6934</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>336.4898249977304</v>
+        <v>363.5354367537494</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>84.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>50.70227816592537</v>
+        <v>67.31572619832953</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>27.01826268468589</v>
+        <v>24.13674768078842</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.022949906104785</v>
+        <v>0.3063228187683225</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>1.047245616248001</v>
+        <v>1.878203271211565</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7768</v>
+        <v>6887</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>324.8221453145448</v>
+        <v>339.2026394759769</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>321.5</v>
+        <v>37.55</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>36.44679651739599</v>
+        <v>55.54526063761976</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>20.81887441150474</v>
+        <v>11.4265929579154</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5072591372671099</v>
+        <v>2.02026394759769</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.233501499123809</v>
+        <v>0.4006171814646344</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, rsi_strong, market_above_ma60, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6951</v>
+        <v>7711</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>323.2991340234359</v>
+        <v>337.4587082196859</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>73.3</v>
+        <v>314</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>32.68710529944127</v>
+        <v>38.7657017355621</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>28.54320661089648</v>
+        <v>23.93324328787323</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4758136566687939</v>
+        <v>0.4203463664556483</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.5206910430798659</v>
+        <v>0.626785165625563</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7820</v>
+        <v>7823</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>319.0823842207301</v>
+        <v>336.4898249977304</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>115</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>41.68386309520953</v>
+        <v>50.70227816592537</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>18.0623397628937</v>
+        <v>27.01826268468589</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2121626629664605</v>
+        <v>1.022949906104785</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.7599035913913013</v>
+        <v>1.047245616248001</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7738</v>
+        <v>7768</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>318.6900060955699</v>
+        <v>324.8221453145448</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>168</v>
+        <v>321.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.95748484803013</v>
+        <v>36.44679651739599</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>25.0961458109996</v>
+        <v>20.81887441150474</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.1608665076141464</v>
+        <v>0.5072591372671099</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0726717325125279</v>
+        <v>-1.233501499123809</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7704</v>
+        <v>6951</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>314.2416761332606</v>
+        <v>323.2991340234359</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>55.4</v>
+        <v>73.3</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>33.92623378211115</v>
+        <v>32.68710529944127</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.49434913253813</v>
+        <v>28.54320661089648</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.41433600519621</v>
+        <v>0.4758136566687939</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.8178400086197459</v>
+        <v>-0.5206910430798659</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6971</v>
+        <v>7820</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>312.1236217012176</v>
+        <v>319.0823842207301</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>27.2</v>
+        <v>115</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45.11596993298824</v>
+        <v>41.68386309520953</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.50296928133043</v>
+        <v>18.0623397628937</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.665843590779589</v>
+        <v>0.2121626629664605</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0593219426954056</v>
+        <v>0.7599035913913013</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6996</v>
+        <v>7738</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>307.4854869068682</v>
+        <v>318.6900060955699</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>180.5</v>
+        <v>168</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>38.88525141924474</v>
+        <v>46.95748484803013</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.42121394531364</v>
+        <v>25.0961458109996</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3261169200814336</v>
+        <v>0.1608665076141464</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-2.417258937282577</v>
+        <v>-0.0726717325125279</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6862</v>
+        <v>7704</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>307.2965690337518</v>
+        <v>314.2416761332606</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>165.5</v>
+        <v>55.4</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>38.71121511534189</v>
+        <v>33.92623378211115</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.30059495942857</v>
+        <v>15.49434913253813</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2244054827966063</v>
+        <v>0.41433600519621</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-3.67381509826333</v>
+        <v>-0.8178400086197459</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6906</v>
+        <v>6971</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>301.2087545316455</v>
+        <v>312.1236217012176</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>27.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>27.97150181576265</v>
+        <v>45.11596993298824</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.62879297461709</v>
+        <v>18.50296928133043</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4217731331522113</v>
+        <v>0.665843590779589</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-2.181138889360646</v>
+        <v>-0.0593219426954056</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6903</v>
+        <v>6996</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>298.1079220948152</v>
+        <v>307.4854869068682</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>395</v>
+        <v>180.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.57446302364944</v>
+        <v>38.88525141924474</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9.358111349190455</v>
+        <v>20.42121394531364</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.802784943529136</v>
+        <v>0.3261169200814336</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>1.223504736630051</v>
+        <v>-2.417258937282577</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8032</v>
+        <v>6862</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>295.6676749176819</v>
+        <v>307.2965690337518</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>39</v>
+        <v>165.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>33.52930940357392</v>
+        <v>38.71121511534189</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.48806152389611</v>
+        <v>16.30059495942857</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.268190406502241</v>
+        <v>0.2244054827966063</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.6358418869947471</v>
+        <v>-3.67381509826333</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6983</v>
+        <v>6906</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>287.3133022615498</v>
+        <v>301.2087545316455</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>354</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.95303034991088</v>
+        <v>27.97150181576265</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.4205216745423</v>
+        <v>20.62879297461709</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.2748357608702138</v>
+        <v>0.4217731331522113</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1.152587974587233</v>
+        <v>-2.181138889360646</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7750</v>
+        <v>6903</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>279.1053282544641</v>
+        <v>298.1079220948152</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>1955</v>
+        <v>395</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>38.57074977081572</v>
+        <v>51.57446302364944</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.22009951074387</v>
+        <v>9.358111349190455</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8225224852365189</v>
+        <v>0.802784943529136</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-9.199276607702082</v>
+        <v>1.223504736630051</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7810</v>
+        <v>8032</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>277.6721935725409</v>
+        <v>295.6676749176819</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>198</v>
+        <v>39</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>39.79817828519313</v>
+        <v>33.52930940357392</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15.27984366408842</v>
+        <v>22.48806152389611</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6256441962661073</v>
+        <v>0.268190406502241</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.5680468116891131</v>
+        <v>-0.6358418869947471</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7744</v>
+        <v>6983</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>271.1296507547282</v>
+        <v>287.3133022615498</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>453</v>
+        <v>354</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>43.92025828483691</v>
+        <v>46.95303034991088</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10.34222652744939</v>
+        <v>10.4205216745423</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.1731592723446062</v>
+        <v>0.2748357608702138</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>1.361251427639143</v>
+        <v>1.152587974587233</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6916</v>
+        <v>7750</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>269.8261939930621</v>
+        <v>279.1053282544641</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>20.3</v>
+        <v>1955</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.74913763996417</v>
+        <v>38.57074977081572</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15.54141142283826</v>
+        <v>16.22009951074387</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3544339217899177</v>
+        <v>0.8225224852365189</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.1223339625798214</v>
+        <v>-9.199276607702082</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6902</v>
+        <v>7810</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>268.7398549882152</v>
+        <v>277.6721935725409</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>48.39333153238716</v>
+        <v>39.79817828519313</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.86626701275146</v>
+        <v>15.27984366408842</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.1212291516978077</v>
+        <v>0.6256441962661073</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.7396970045612596</v>
+        <v>0.5680468116891131</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7822</v>
+        <v>7744</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>266.5517772725374</v>
+        <v>271.1296507547282</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>963</v>
+        <v>453</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>40.16235090133639</v>
+        <v>43.92025828483691</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17.66635717184905</v>
+        <v>10.34222652744939</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.469832128287792</v>
+        <v>0.1731592723446062</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-16.07275262332774</v>
+        <v>1.361251427639143</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7792</v>
+        <v>6916</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>262.302856310892</v>
+        <v>269.8261939930621</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>226.5</v>
+        <v>20.3</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>32.90309572947749</v>
+        <v>50.74913763996417</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>21.73114925423634</v>
+        <v>15.54141142283826</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4885481490986078</v>
+        <v>0.3544339217899177</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-1.460246774139613</v>
+        <v>-0.1223339625798214</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7842</v>
+        <v>6902</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>259.5923900160297</v>
+        <v>268.7398549882152</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>8.700528265088096</v>
+        <v>48.39333153238716</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>21.57372617393307</v>
+        <v>15.86626701275146</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.0288892658927316</v>
+        <v>0.1212291516978077</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-5.312345605274487</v>
+        <v>-0.7396970045612596</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7805</v>
+        <v>7822</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>259.3731831601796</v>
+        <v>266.5517772725374</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>623</v>
+        <v>963</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>31.16969790580193</v>
+        <v>40.16235090133639</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>34.38926499060859</v>
+        <v>17.66635717184905</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2858385558299703</v>
+        <v>0.469832128287792</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-2.2840271455288</v>
+        <v>-16.07275262332774</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7732</v>
+        <v>7792</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>254.6039920527869</v>
+        <v>262.302856310892</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>35.65</v>
+        <v>226.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>51.73773387166454</v>
+        <v>32.90309572947749</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>8.942432006978338</v>
+        <v>21.73114925423634</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.342219088321538</v>
+        <v>0.4885481490986078</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.8379134717803733</v>
+        <v>-1.460246774139613</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6958</v>
+        <v>7842</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>252.1165486551442</v>
+        <v>259.5923900160297</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>17.95</v>
+        <v>0</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>58.97001815006946</v>
+        <v>8.700528265088096</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.48063995282772</v>
+        <v>21.57372617393307</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.232500974552564</v>
+        <v>0.0288892658927316</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.1691492084968183</v>
+        <v>-5.312345605274487</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7740</v>
+        <v>7805</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>248.0177473199206</v>
+        <v>259.3731831601796</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>158.5</v>
+        <v>623</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.39719286006096</v>
+        <v>31.16969790580193</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>17.07994627283703</v>
+        <v>34.38926499060859</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7033746846193801</v>
+        <v>0.2858385558299703</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.914521874001796</v>
+        <v>-2.2840271455288</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7760</v>
+        <v>7732</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>244.5284844373681</v>
+        <v>254.6039920527869</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>34.05</v>
+        <v>35.65</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.10934885876801</v>
+        <v>51.73773387166454</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>29.49235761215802</v>
+        <v>8.942432006978338</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6145649494178798</v>
+        <v>1.342219088321538</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0292168458635204</v>
+        <v>0.8379134717803733</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6859</v>
+        <v>6958</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>241.6313650278848</v>
+        <v>252.1165486551442</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>105.5</v>
+        <v>17.95</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>28.50749440994333</v>
+        <v>58.97001815006946</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21.21296519181515</v>
+        <v>16.48063995282772</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.26991949261201</v>
+        <v>1.232500974552564</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-2.262624828569245</v>
+        <v>0.1691492084968183</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7703</v>
+        <v>7740</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>239.0680514276303</v>
+        <v>248.0177473199206</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>196</v>
+        <v>158.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45.52237769987472</v>
+        <v>51.39719286006096</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10.75296494312416</v>
+        <v>17.07994627283703</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.206971909729785</v>
+        <v>0.7033746846193801</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0433703910633891</v>
+        <v>1.914521874001796</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6899</v>
+        <v>7760</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>235.5638624237736</v>
+        <v>244.5284844373681</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>52.2</v>
+        <v>34.05</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>28.1938257614996</v>
+        <v>49.10934885876801</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.64030726257924</v>
+        <v>29.49235761215802</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.3146551453982129</v>
+        <v>0.6145649494178798</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.6593987088962505</v>
+        <v>-0.0292168458635204</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7728</v>
+        <v>6859</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>234.0237354446501</v>
+        <v>241.6313650278848</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>688</v>
+        <v>105.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.71895556460267</v>
+        <v>28.50749440994333</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>10.9801319992427</v>
+        <v>21.21296519181515</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3127728714644148</v>
+        <v>0.26991949261201</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>4.117002715544746</v>
+        <v>-2.262624828569245</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7721</v>
+        <v>7703</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>229.4121524588544</v>
+        <v>239.0680514276303</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>65.59999999999999</v>
+        <v>196</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>36.52494289016504</v>
+        <v>45.52237769987472</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>10.72984497675288</v>
+        <v>10.75296494312416</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.2772208330331396</v>
+        <v>0.206971909729785</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.5773522940472557</v>
+        <v>-0.0433703910633891</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7753</v>
+        <v>6899</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>228.6532668861213</v>
+        <v>235.5638624237736</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>40.8</v>
+        <v>52.2</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>40.91224657690942</v>
+        <v>28.1938257614996</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>24.08969811481227</v>
+        <v>19.64030726257924</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.25497931654345</v>
+        <v>0.3146551453982129</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.2153739672552626</v>
+        <v>-0.6593987088962505</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6965</v>
+        <v>7728</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>226.8772521549123</v>
+        <v>234.0237354446501</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>79.3</v>
+        <v>688</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.02113392200658</v>
+        <v>50.71895556460267</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>25.0677582966255</v>
+        <v>10.9801319992427</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4242657484762102</v>
+        <v>0.3127728714644148</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1682777822964647</v>
+        <v>4.117002715544746</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6952</v>
+        <v>7721</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>226.5175356654957</v>
+        <v>229.4121524588544</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>35.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>50.37878057798552</v>
+        <v>36.52494289016504</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.38978116992094</v>
+        <v>10.72984497675288</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.390950648069378</v>
+        <v>0.2772208330331396</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0568298849428398</v>
+        <v>-0.5773522940472557</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6922</v>
+        <v>7753</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>224.5146752564052</v>
+        <v>228.6532668861213</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>171.5</v>
+        <v>40.8</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>40.91021453275549</v>
+        <v>40.91224657690942</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13.82293045244365</v>
+        <v>24.08969811481227</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6849371212201338</v>
+        <v>0.25497931654345</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.3674339599521325</v>
+        <v>-0.2153739672552626</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6910</v>
+        <v>6965</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>221.4173946631823</v>
+        <v>226.8772521549123</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>25.8</v>
+        <v>79.3</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>29.01679739624953</v>
+        <v>49.02113392200658</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>20.79969231412473</v>
+        <v>25.0677582966255</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3908260265858797</v>
+        <v>0.4242657484762102</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.1404069423950335</v>
+        <v>0.1682777822964647</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7749</v>
+        <v>6952</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>220.3599590380729</v>
+        <v>226.5175356654957</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>387</v>
+        <v>35.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>32.10144445752168</v>
+        <v>50.37878057798552</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>18.53212167915593</v>
+        <v>14.38978116992094</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.2934828842890196</v>
+        <v>1.390950648069378</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-3.567696180950144</v>
+        <v>0.0568298849428398</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7772</v>
+        <v>6922</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>220.1614314128284</v>
+        <v>224.5146752564052</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>104</v>
+        <v>171.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>29.94027375492993</v>
+        <v>40.91021453275549</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>13.91476823131159</v>
+        <v>13.82293045244365</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7638842833281434</v>
+        <v>0.6849371212201338</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-1.960529089654097</v>
+        <v>-0.3674339599521325</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7556</v>
+        <v>6910</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>214.4223680159032</v>
+        <v>221.4173946631823</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>232.5</v>
+        <v>25.8</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>29.53075973846197</v>
+        <v>29.01679739624953</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18.91181567888439</v>
+        <v>20.79969231412473</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5680554033095685</v>
+        <v>0.3908260265858797</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-6.228113585639468</v>
+        <v>-0.1404069423950335</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6925</v>
+        <v>7749</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>212.2625470927049</v>
+        <v>220.3599590380729</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>57.2</v>
+        <v>387</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.83017430737105</v>
+        <v>32.10144445752168</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>10.546285884349</v>
+        <v>18.53212167915593</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.1408923365070746</v>
+        <v>0.2934828842890196</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.2778253315229979</v>
+        <v>-3.567696180950144</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6955</v>
+        <v>7772</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>211.4693947678948</v>
+        <v>220.1614314128284</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.32932911249322</v>
+        <v>29.94027375492993</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>6.219279220274749</v>
+        <v>13.91476823131159</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4704459369131362</v>
+        <v>0.7638842833281434</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.8908437897017221</v>
+        <v>-1.960529089654097</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6877</v>
+        <v>7556</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>210.9260209871919</v>
+        <v>214.4223680159032</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>136.5</v>
+        <v>232.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.68677712412626</v>
+        <v>29.53075973846197</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.45400554707441</v>
+        <v>18.91181567888439</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.1747229366028153</v>
+        <v>0.5680554033095685</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>1</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>1.565261034837449</v>
+        <v>-6.228113585639468</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7769</v>
+        <v>6925</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>210.8641690588006</v>
+        <v>212.2625470927049</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>6695</v>
+        <v>57.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>49.53376738566158</v>
+        <v>39.83017430737105</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.29919763184277</v>
+        <v>10.546285884349</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.7287597079016521</v>
+        <v>0.1408923365070746</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-9.57024065417464</v>
+        <v>-0.2778253315229979</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6885</v>
+        <v>6955</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>205.1145036780693</v>
+        <v>211.4693947678948</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>21.65</v>
+        <v>113</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.11816873457806</v>
+        <v>47.32932911249322</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.85476487663193</v>
+        <v>6.219279220274749</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.7190552351474949</v>
+        <v>0.4704459369131362</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.047384426260512</v>
+        <v>0.8908437897017221</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6924</v>
+        <v>6877</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>203.9264002957618</v>
+        <v>210.9260209871919</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>116</v>
+        <v>136.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.49742254508995</v>
+        <v>50.68677712412626</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.80241098953693</v>
+        <v>12.45400554707441</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.446158112321686</v>
+        <v>0.1747229366028153</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.3189464798278125</v>
+        <v>1.565261034837449</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6909</v>
+        <v>7769</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>202.5743600031385</v>
+        <v>210.8641690588006</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>46.9</v>
+        <v>6695</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>38.48178260145405</v>
+        <v>49.53376738566158</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.24969591764083</v>
+        <v>12.29919763184277</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.2308895369212465</v>
+        <v>0.7287597079016521</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.214895030759528</v>
+        <v>-9.57024065417464</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6890</v>
+        <v>6885</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>201.715659579315</v>
+        <v>205.1145036780693</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>172.5</v>
+        <v>21.65</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>36.5070617740812</v>
+        <v>47.11816873457806</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>18.09780147207356</v>
+        <v>15.85476487663193</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7519835687282301</v>
+        <v>0.7190552351474949</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-6.19683041881504</v>
+        <v>0.047384426260512</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8034</v>
+        <v>6924</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>200.50253788614</v>
+        <v>203.9264002957618</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>19.85</v>
+        <v>116</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>21.05869036899757</v>
+        <v>42.49742254508995</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>29.35806793446043</v>
+        <v>13.80241098953693</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7183109650479578</v>
+        <v>0.446158112321686</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1957001323261123</v>
+        <v>-0.3189464798278125</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7547</v>
+        <v>6909</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>198.1430348035883</v>
+        <v>202.5743600031385</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>54.8</v>
+        <v>46.9</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>35.6863439892314</v>
+        <v>38.48178260145405</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.47279169902891</v>
+        <v>17.24969591764083</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3155799537096848</v>
+        <v>0.2308895369212465</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.020954638422822</v>
+        <v>-1.214895030759528</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6962</v>
+        <v>6890</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>191.2685489704612</v>
+        <v>201.715659579315</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>34.3</v>
+        <v>172.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>39.66908538632507</v>
+        <v>36.5070617740812</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>16.04835343358299</v>
+        <v>18.09780147207356</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.2991558393683254</v>
+        <v>0.7519835687282301</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.5134551773611905</v>
+        <v>-6.19683041881504</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6894</v>
+        <v>8034</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>189.5679263902074</v>
+        <v>200.50253788614</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>348</v>
+        <v>19.85</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.69709364544042</v>
+        <v>21.05869036899757</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.92316521427586</v>
+        <v>29.35806793446043</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2761974056611333</v>
+        <v>0.7183109650479578</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.952654693311192</v>
+        <v>-0.1957001323261123</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7765</v>
+        <v>7547</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>184.2417522914765</v>
+        <v>198.1430348035883</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>226</v>
+        <v>54.8</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.82311946051016</v>
+        <v>35.6863439892314</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.54489143588187</v>
+        <v>12.47279169902891</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.7406123990140062</v>
+        <v>0.3155799537096848</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.7579529819798871</v>
+        <v>-0.020954638422822</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6865</v>
+        <v>6962</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>184.167830618805</v>
+        <v>191.2685489704612</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>25.4</v>
+        <v>34.3</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>49.64290976076941</v>
+        <v>39.66908538632507</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.12349855246463</v>
+        <v>16.04835343358299</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5046640450813348</v>
+        <v>0.2991558393683254</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0002299249950337</v>
+        <v>-0.5134551773611905</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6969</v>
+        <v>6894</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>182.7082067777333</v>
+        <v>189.5679263902074</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>25.7</v>
+        <v>348</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.77381425380621</v>
+        <v>44.69709364544042</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>20.28678865905403</v>
+        <v>14.92316521427586</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.1629900824036967</v>
+        <v>0.2761974056611333</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.1957092266136653</v>
+        <v>-1.952654693311192</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6854</v>
+        <v>7765</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>178.8893682822953</v>
+        <v>184.2417522914765</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>108</v>
+        <v>226</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>29.16017260564768</v>
+        <v>45.82311946051016</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>29.0789146759819</v>
+        <v>17.54489143588187</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.616151442773258</v>
+        <v>0.7406123990140062</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.8250195689952449</v>
+        <v>0.7579529819798871</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7705</v>
+        <v>6865</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>178.5798634152913</v>
+        <v>184.167830618805</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>31.25</v>
+        <v>25.4</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.28097122648657</v>
+        <v>49.64290976076941</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>18.25784868136041</v>
+        <v>13.12349855246463</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5593132212730447</v>
+        <v>0.5046640450813348</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0714000348066155</v>
+        <v>0.0002299249950337</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6895</v>
+        <v>6969</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>171.6774102114517</v>
+        <v>182.7082067777333</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>129</v>
+        <v>25.7</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>30.43123019689109</v>
+        <v>48.77381425380621</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>24.93720211397148</v>
+        <v>20.28678865905403</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4841367301862367</v>
+        <v>0.1629900824036967</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-1.936452875583562</v>
+        <v>0.1957092266136653</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6855</v>
+        <v>6854</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>170.2199037205203</v>
+        <v>178.8893682822953</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>118.5</v>
+        <v>108</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>51.48785775523771</v>
+        <v>29.16017260564768</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>9.31103807709396</v>
+        <v>29.0789146759819</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.1807141824490385</v>
+        <v>0.616151442773258</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.8149300768293986</v>
+        <v>-0.8250195689952449</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7736</v>
+        <v>7705</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>160.9291337271578</v>
+        <v>178.5798634152913</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>70.8</v>
+        <v>31.25</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>45.36213048170143</v>
+        <v>48.28097122648657</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.36486504911943</v>
+        <v>18.25784868136041</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7726216506038407</v>
+        <v>0.5593132212730447</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.08832445708890339</v>
+        <v>-0.0714000348066155</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6931</v>
+        <v>6895</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>143.9017055520555</v>
+        <v>171.6774102114517</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>39.6</v>
+        <v>129</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>41.17251439512849</v>
+        <v>30.43123019689109</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.90254288021962</v>
+        <v>24.93720211397148</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.6309952280997116</v>
+        <v>0.4841367301862367</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0352860713339616</v>
+        <v>-1.936452875583562</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8044</v>
+        <v>6855</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>142.4089188899293</v>
+        <v>170.2199037205203</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>27.05</v>
+        <v>118.5</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.19812022377985</v>
+        <v>51.48785775523771</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.49734120283717</v>
+        <v>9.31103807709396</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2665843177320799</v>
+        <v>0.1807141824490385</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2131882720059396</v>
+        <v>-0.8149300768293986</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7780</v>
+        <v>7736</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>132.1360473525624</v>
+        <v>160.9291337271578</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>17.9</v>
+        <v>70.8</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>43.93784686178742</v>
+        <v>45.36213048170143</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.67512282187305</v>
+        <v>16.36486504911943</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5629811688914892</v>
+        <v>0.7726216506038407</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0197129111789746</v>
+        <v>0.08832445708890339</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7730</v>
+        <v>6931</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>127.5316948671078</v>
+        <v>143.9017055520555</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>180</v>
+        <v>39.6</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46.78844177384172</v>
+        <v>41.17251439512849</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>11.47199389536575</v>
+        <v>13.90254288021962</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.757786514898274</v>
+        <v>0.6309952280997116</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.4113808339266973</v>
+        <v>0.0352860713339616</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6918</v>
+        <v>8044</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>126.6341183860037</v>
+        <v>142.4089188899293</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>72.8</v>
+        <v>27.05</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>44.42217757088533</v>
+        <v>44.19812022377985</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>16.33328595363181</v>
+        <v>13.49734120283717</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.562630678578217</v>
+        <v>0.2665843177320799</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0024487840611449</v>
+        <v>-0.2131882720059396</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6936</v>
+        <v>7780</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>105.5704726477106</v>
+        <v>132.1360473525624</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>32.7</v>
+        <v>17.9</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>47.54517303990172</v>
+        <v>43.93784686178742</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.47816813900353</v>
+        <v>16.67512282187305</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.100028840293936</v>
+        <v>0.5629811688914892</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0033386981216561</v>
+        <v>-0.0197129111789746</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6988</v>
+        <v>7730</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>101.9516008196034</v>
+        <v>127.5316948671078</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>13.3</v>
+        <v>180</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>37.12527225919587</v>
+        <v>46.78844177384172</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>10.90938023492119</v>
+        <v>11.47199389536575</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.58507307443297</v>
+        <v>0.757786514898274</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.0463108049357681</v>
+        <v>-0.4113808339266973</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6908</v>
+        <v>6918</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>99.29156446963501</v>
+        <v>126.6341183860037</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>36.05</v>
+        <v>72.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>34.22014520731643</v>
+        <v>44.42217757088533</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>19.15279251334683</v>
+        <v>16.33328595363181</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.475963826749167</v>
+        <v>0.562630678578217</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0687401023760974</v>
+        <v>-0.0024487840611449</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6933</v>
+        <v>6936</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>85.63869989337083</v>
+        <v>105.5704726477106</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>161.5</v>
+        <v>32.7</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>53.17234448482395</v>
+        <v>47.54517303990172</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>15.83044323430825</v>
+        <v>15.47816813900353</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.3869802001133</v>
+        <v>1.100028840293936</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>2.883457877641065</v>
+        <v>-0.0033386981216561</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>8011</v>
+        <v>6988</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>82.27773743637302</v>
+        <v>101.9516008196034</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>16.85</v>
+        <v>13.3</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>39.4865077426799</v>
+        <v>37.12527225919587</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.64028624194223</v>
+        <v>10.90938023492119</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.3828197457346587</v>
+        <v>0.58507307443297</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0448814991479827</v>
+        <v>0.0463108049357681</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7803</v>
+        <v>6908</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>67.99534758195091</v>
+        <v>99.29156446963501</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>22.6</v>
+        <v>36.05</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>43.75260021697634</v>
+        <v>34.22014520731643</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>12.96592453297325</v>
+        <v>19.15279251334683</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.3831388630157797</v>
+        <v>0.475963826749167</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0850470217359118</v>
+        <v>-0.0687401023760974</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>8038</v>
+        <v>6933</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>61.04842238914249</v>
+        <v>85.63869989337083</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>39.35</v>
+        <v>161.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>46.33765646819796</v>
+        <v>53.17234448482395</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>18.861721707316</v>
+        <v>15.83044323430825</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.4841965493852768</v>
+        <v>1.3869802001133</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,62 +7142,221 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1506593414201855</v>
+        <v>2.883457877641065</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>8011</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>台通</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>82.27773743637302</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>39.4865077426799</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>17.64028624194223</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.3828197457346587</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.0448814991479827</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>7803</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>雲象科技-創</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>67.99534758195091</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>43.75260021697634</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>12.96592453297325</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.3831388630157797</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.0850470217359118</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>8038</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>長園科</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>61.04842238914249</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>46.33765646819796</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>18.861721707316</v>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.4841965493852768</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>-0.1506593414201855</v>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
         <v>6921</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>嘉雨思-創</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
+      <c r="C130" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D130" s="2" t="n">
         <v>48.29516592223635</v>
       </c>
-      <c r="E127" s="2" t="n">
+      <c r="E130" s="2" t="n">
         <v>67.8</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H130" s="2" t="n">
         <v>42.08731397554629</v>
       </c>
-      <c r="I127" s="2" t="n">
+      <c r="I130" s="2" t="n">
         <v>19.91821831153753</v>
       </c>
-      <c r="J127" s="2" t="n">
+      <c r="J130" s="2" t="n">
         <v>0.3048110239087833</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
+      <c r="K130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" s="2" t="n">
         <v>0.2353142983316762</v>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O130" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
